--- a/SeleniumTests/TestDataFolder/CustomerTestDataNegative.xlsx
+++ b/SeleniumTests/TestDataFolder/CustomerTestDataNegative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924DC538-9BCC-4363-8FA6-33664382D813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8D4CFF-4B21-43A5-B8B3-91E3FE2E7FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BlankMandatoryFieldsTestData" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="47">
   <si>
     <t>Petaling Jaya</t>
   </si>
@@ -47,51 +47,6 @@
     <t>Lorong 333, Taman 444</t>
   </si>
   <si>
-    <t>Custname</t>
-  </si>
-  <si>
-    <t>CustTinNumber</t>
-  </si>
-  <si>
-    <t>BEregisterType</t>
-  </si>
-  <si>
-    <t>CustRegisterID</t>
-  </si>
-  <si>
-    <t>Custsst</t>
-  </si>
-  <si>
-    <t>CustEmail</t>
-  </si>
-  <si>
-    <t>CustContactNumber</t>
-  </si>
-  <si>
-    <t>CustCity</t>
-  </si>
-  <si>
-    <t>CustState</t>
-  </si>
-  <si>
-    <t>CustPosCode</t>
-  </si>
-  <si>
-    <t>CustCountry</t>
-  </si>
-  <si>
-    <t>CustAddress1</t>
-  </si>
-  <si>
-    <t>CustAddress2</t>
-  </si>
-  <si>
-    <t>CustAddress3</t>
-  </si>
-  <si>
-    <t>CustExternalCode</t>
-  </si>
-  <si>
     <t>QUBE APPS SOLUTIONS SDN BHD</t>
   </si>
   <si>
@@ -119,15 +74,9 @@
     <t>Perindustrian 555</t>
   </si>
   <si>
-    <t>CustomerCode</t>
-  </si>
-  <si>
     <t>CUST_000002</t>
   </si>
   <si>
-    <t>scenario</t>
-  </si>
-  <si>
     <t>BlankMandatoryFields</t>
   </si>
   <si>
@@ -149,9 +98,6 @@
     <t>Ext12345</t>
   </si>
   <si>
-    <t>filePath</t>
-  </si>
-  <si>
     <t>D:\\e-invoice\\SeleniumTests\\InvalidFileType\\TestInvalidFileType.txt</t>
   </si>
   <si>
@@ -171,6 +117,63 @@
   </si>
   <si>
     <t>InvalidTIN1</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Customer Tin Number</t>
+  </si>
+  <si>
+    <t>Customer Register Type</t>
+  </si>
+  <si>
+    <t>Customer Register ID</t>
+  </si>
+  <si>
+    <t>Customer SST</t>
+  </si>
+  <si>
+    <t>Customer Email</t>
+  </si>
+  <si>
+    <t>Customer Contact Number</t>
+  </si>
+  <si>
+    <t>Customer City</t>
+  </si>
+  <si>
+    <t>Customer State</t>
+  </si>
+  <si>
+    <t>Customer Pos Code</t>
+  </si>
+  <si>
+    <t>Customer Country</t>
+  </si>
+  <si>
+    <t>Customer Address1</t>
+  </si>
+  <si>
+    <t>Custommer Address2</t>
+  </si>
+  <si>
+    <t>Customer Address3</t>
+  </si>
+  <si>
+    <t>Customer External Code</t>
+  </si>
+  <si>
+    <t>Test Scenario</t>
+  </si>
+  <si>
+    <t>Customer Address2</t>
+  </si>
+  <si>
+    <t>Customer Code</t>
+  </si>
+  <si>
+    <t>Import File Path</t>
   </si>
 </sst>
 </file>
@@ -503,64 +506,78 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F2" s="2"/>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -573,79 +590,97 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0B0841-31B9-4240-9153-94BA6D6BD076}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="30.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1"/>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -660,84 +695,102 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E6B15F-5627-44EC-BF12-8E86D94EC5BB}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>12345</v>
@@ -752,10 +805,10 @@
         <v>3</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -770,84 +823,102 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE8BCEDC-0171-435D-90EB-2A4C9CED6347}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>12345</v>
@@ -862,13 +933,13 @@
         <v>3</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="P2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -883,81 +954,98 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521284FB-BF33-4DDA-9A26-634485D4EAAE}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="N1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="O1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>12345</v>
@@ -972,10 +1060,10 @@
         <v>3</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -990,69 +1078,86 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F9ADD3D-339B-4C06-87FB-A577E78E3578}">
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="L1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="O1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="P1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1"/>
       <c r="G2" s="2"/>
       <c r="H2" s="1"/>
       <c r="Q2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1064,90 +1169,109 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F46C7B-49FE-4FD0-B59C-D9F8FBF3C627}">
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="L1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="O1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="P1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>12345</v>
@@ -1162,10 +1286,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1180,90 +1304,109 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B78921C3-68E8-4772-A21E-5D0ECAD155F1}">
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="J1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="L1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="M1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N1" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="O1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="P1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>12345</v>
@@ -1278,13 +1421,13 @@
         <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1299,30 +1442,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D179B8DB-90B3-4EF3-896B-CE5D22D4407F}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="66.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
